--- a/development/one_file_rosetta_output/CPCT02010772T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/CPCT02010772T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E520"/>
+  <dimension ref="A1:F520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -734,7 +755,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -762,7 +786,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -790,7 +817,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -816,9 +846,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -934,7 +967,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -990,7 +1026,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1018,7 +1057,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1089,7 +1131,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1182,7 +1227,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1210,7 +1258,10 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1264,9 +1315,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>5</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1320,9 +1374,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1378,7 +1435,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1441,7 +1501,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1502,9 +1565,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>98</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1558,9 +1624,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>98</v>
+      </c>
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1614,9 +1683,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>98</v>
+      </c>
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1670,9 +1742,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>98</v>
+      </c>
+      <c r="E24" s="4">
         <v>4</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1726,9 +1801,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>98</v>
+      </c>
+      <c r="E25" s="4">
         <v>5</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1782,9 +1860,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>2</v>
+      </c>
+      <c r="E26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1838,9 +1919,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>21</v>
+      </c>
+      <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1901,9 +1985,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>21</v>
+      </c>
+      <c r="E28" s="4">
         <v>2</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1964,9 +2051,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>21</v>
+      </c>
+      <c r="E29" s="4">
         <v>3</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2027,9 +2117,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>21</v>
+      </c>
+      <c r="E30" s="4">
         <v>4</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2090,9 +2183,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>21</v>
+      </c>
+      <c r="E31" s="4">
         <v>5</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2153,9 +2249,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>7</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2224,9 +2323,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>7</v>
+      </c>
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2295,9 +2397,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2368,7 +2473,10 @@
       <c r="D35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2394,9 +2502,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2472,9 +2583,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>5</v>
+      </c>
+      <c r="E37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2550,9 +2664,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4">
         <v>3</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2630,7 +2747,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2656,9 +2776,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2734,9 +2857,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>14</v>
+      </c>
+      <c r="E41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2820,9 +2946,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>14</v>
+      </c>
+      <c r="E42" s="4">
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2906,9 +3035,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>14</v>
+      </c>
+      <c r="E43" s="4">
         <v>3</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2992,9 +3124,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>14</v>
+      </c>
+      <c r="E44" s="4">
         <v>4</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3078,9 +3213,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>14</v>
+      </c>
+      <c r="E45" s="4">
         <v>5</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3164,9 +3302,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>6</v>
+      </c>
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3250,9 +3391,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>6</v>
+      </c>
+      <c r="E47" s="4">
         <v>2</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3336,9 +3480,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4">
         <v>3</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3422,9 +3569,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>6</v>
+      </c>
+      <c r="E49" s="4">
         <v>4</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3508,9 +3658,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>7</v>
+      </c>
+      <c r="E50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3594,9 +3747,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>7</v>
+      </c>
+      <c r="E51" s="4">
         <v>2</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3680,9 +3836,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3773,9 +3932,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3866,9 +4028,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3961,7 +4126,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3987,9 +4155,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>2</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4090,7 +4261,10 @@
       <c r="D57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>2</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4189,9 +4363,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>2</v>
+      </c>
+      <c r="E58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4292,7 +4469,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4400,7 +4580,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4426,9 +4609,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>4</v>
+      </c>
+      <c r="E61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4534,9 +4720,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>4</v>
+      </c>
+      <c r="E62" s="4">
         <v>2</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4644,7 +4833,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4672,7 +4864,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4786,9 +4981,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>15</v>
+      </c>
+      <c r="E65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4842,9 +5040,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>15</v>
+      </c>
+      <c r="E66" s="4">
         <v>2</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4898,9 +5099,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>15</v>
+      </c>
+      <c r="E67" s="4">
         <v>3</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4954,9 +5158,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>15</v>
+      </c>
+      <c r="E68" s="4">
         <v>4</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5010,9 +5217,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>15</v>
+      </c>
+      <c r="E69" s="4">
         <v>5</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5068,7 +5278,10 @@
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5122,9 +5335,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>4</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5178,9 +5394,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>14</v>
+      </c>
+      <c r="E72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5241,9 +5460,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>14</v>
+      </c>
+      <c r="E73" s="4">
         <v>2</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5304,9 +5526,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>14</v>
+      </c>
+      <c r="E74" s="4">
         <v>3</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5367,9 +5592,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>14</v>
+      </c>
+      <c r="E75" s="4">
         <v>4</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5430,9 +5658,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>14</v>
+      </c>
+      <c r="E76" s="4">
         <v>5</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5493,9 +5724,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5558,7 +5792,10 @@
       <c r="D78" s="4">
         <v>2</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>2</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5619,9 +5856,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>6</v>
+      </c>
+      <c r="E79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5697,9 +5937,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>6</v>
+      </c>
+      <c r="E80" s="4">
         <v>2</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5775,9 +6018,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>6</v>
+      </c>
+      <c r="E81" s="4">
         <v>3</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5853,9 +6099,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>6</v>
+      </c>
+      <c r="E82" s="4">
         <v>4</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5931,9 +6180,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>6</v>
+      </c>
+      <c r="E83" s="4">
         <v>5</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6009,9 +6261,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>4</v>
+      </c>
+      <c r="E84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6087,9 +6342,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>4</v>
+      </c>
+      <c r="E85" s="4">
         <v>2</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6165,9 +6423,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>3</v>
+      </c>
+      <c r="E86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6251,9 +6512,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>3</v>
+      </c>
+      <c r="E87" s="4">
         <v>2</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6337,9 +6601,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>3</v>
+      </c>
+      <c r="E88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6423,9 +6690,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>3</v>
+      </c>
+      <c r="E89" s="4">
         <v>2</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6509,9 +6779,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>2</v>
+      </c>
+      <c r="E90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6595,9 +6868,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6688,9 +6964,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>4</v>
+      </c>
+      <c r="E92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6781,9 +7060,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>4</v>
+      </c>
+      <c r="E93" s="4">
         <v>2</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6876,7 +7158,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6967,9 +7252,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>4</v>
+      </c>
+      <c r="E95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6995,9 +7283,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>2</v>
+      </c>
+      <c r="E96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7096,9 +7387,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>2</v>
+      </c>
+      <c r="E97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7199,7 +7493,10 @@
       <c r="D98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7227,7 +7524,10 @@
       <c r="D99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7253,9 +7553,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>21</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7309,9 +7612,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>21</v>
+      </c>
+      <c r="E101" s="4">
         <v>2</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7365,9 +7671,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>21</v>
+      </c>
+      <c r="E102" s="4">
         <v>3</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7421,9 +7730,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>21</v>
+      </c>
+      <c r="E103" s="4">
         <v>4</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7477,9 +7789,12 @@
         </is>
       </c>
       <c r="D104" s="4">
+        <v>21</v>
+      </c>
+      <c r="E104" s="4">
         <v>5</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7535,7 +7850,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7561,9 +7879,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>11</v>
+      </c>
+      <c r="E106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7624,9 +7945,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>11</v>
+      </c>
+      <c r="E107" s="4">
         <v>2</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7687,9 +8011,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>11</v>
+      </c>
+      <c r="E108" s="4">
         <v>3</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7750,9 +8077,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>11</v>
+      </c>
+      <c r="E109" s="4">
         <v>4</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7813,9 +8143,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>11</v>
+      </c>
+      <c r="E110" s="4">
         <v>5</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7876,9 +8209,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>2</v>
+      </c>
+      <c r="E111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7941,7 +8277,10 @@
       <c r="D112" s="4">
         <v>2</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>2</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8002,9 +8341,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>4</v>
+      </c>
+      <c r="E113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8073,9 +8415,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>4</v>
+      </c>
+      <c r="E114" s="4">
         <v>2</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8144,9 +8489,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>4</v>
+      </c>
+      <c r="E115" s="4">
         <v>3</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8217,7 +8565,10 @@
       <c r="D116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8243,9 +8594,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>4</v>
+      </c>
+      <c r="E117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8321,9 +8675,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>1</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8401,7 +8758,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8427,9 +8787,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>2</v>
+      </c>
+      <c r="E120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8515,7 +8878,10 @@
       <c r="D121" s="4">
         <v>2</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>2</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8601,7 +8967,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8629,7 +8998,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8655,9 +9027,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>4</v>
+      </c>
+      <c r="E124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8748,9 +9123,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>4</v>
+      </c>
+      <c r="E125" s="4">
         <v>2</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8843,7 +9221,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8871,7 +9252,10 @@
       <c r="D127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8972,7 +9356,10 @@
       <c r="D128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9073,7 +9460,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9101,7 +9491,10 @@
       <c r="D130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9129,7 +9522,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9157,7 +9553,10 @@
       <c r="D132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9183,9 +9582,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>2</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9299,9 +9701,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>5</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9357,7 +9762,10 @@
       <c r="D135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9413,7 +9821,10 @@
       <c r="D136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9489,9 +9900,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>2</v>
+      </c>
+      <c r="E137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9519,7 +9933,10 @@
       <c r="D138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9573,9 +9990,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>2</v>
+      </c>
+      <c r="E139" s="4">
         <v>1</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9631,7 +10051,10 @@
       <c r="D140" s="4">
         <v>2</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="4">
+        <v>2</v>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9685,9 +10108,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>2</v>
+      </c>
+      <c r="E141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9743,7 +10169,10 @@
       <c r="D142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9771,7 +10200,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9849,7 +10281,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9935,7 +10370,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9963,7 +10401,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10071,7 +10512,10 @@
       <c r="D147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10192,9 +10636,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>10</v>
+      </c>
+      <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10248,9 +10695,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>10</v>
+      </c>
+      <c r="E149" s="4">
         <v>2</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10304,9 +10754,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>10</v>
+      </c>
+      <c r="E150" s="4">
         <v>3</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10360,9 +10813,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>10</v>
+      </c>
+      <c r="E151" s="4">
         <v>4</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10416,9 +10872,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>2</v>
+      </c>
+      <c r="E152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10444,9 +10903,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>3</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10507,9 +10969,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>3</v>
+      </c>
+      <c r="E154" s="4">
         <v>2</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10572,7 +11037,10 @@
       <c r="D155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="4">
+        <v>1</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10600,7 +11068,10 @@
       <c r="D156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10626,9 +11097,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>2</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10714,7 +11188,10 @@
       <c r="D158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="4">
+        <v>2</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10800,7 +11277,10 @@
       <c r="D159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10901,7 +11381,10 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11015,9 +11498,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>19</v>
+      </c>
+      <c r="E161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11071,9 +11557,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>19</v>
+      </c>
+      <c r="E162" s="4">
         <v>2</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11127,9 +11616,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>19</v>
+      </c>
+      <c r="E163" s="4">
         <v>3</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11183,9 +11675,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>2</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11241,7 +11736,10 @@
       <c r="D165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>1</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11267,9 +11765,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>2</v>
+      </c>
+      <c r="E166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11330,9 +11831,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>13</v>
+      </c>
+      <c r="E167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11401,9 +11905,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>13</v>
+      </c>
+      <c r="E168" s="4">
         <v>2</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11472,9 +11979,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>13</v>
+      </c>
+      <c r="E169" s="4">
         <v>3</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11543,9 +12053,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>13</v>
+      </c>
+      <c r="E170" s="4">
         <v>4</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11614,9 +12127,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>13</v>
+      </c>
+      <c r="E171" s="4">
         <v>5</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11685,9 +12201,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>8</v>
+      </c>
+      <c r="E172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11763,9 +12282,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>8</v>
+      </c>
+      <c r="E173" s="4">
         <v>2</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11841,9 +12363,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>8</v>
+      </c>
+      <c r="E174" s="4">
         <v>3</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11919,9 +12444,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>8</v>
+      </c>
+      <c r="E175" s="4">
         <v>4</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11997,9 +12525,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>8</v>
+      </c>
+      <c r="E176" s="4">
         <v>5</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12075,9 +12606,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>3</v>
+      </c>
+      <c r="E177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12161,9 +12695,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>3</v>
+      </c>
+      <c r="E178" s="4">
         <v>2</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12247,9 +12784,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>2</v>
+      </c>
+      <c r="E179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12342,7 +12882,10 @@
       <c r="D180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>1</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12435,7 +12978,10 @@
       <c r="D181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="4">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12461,9 +13007,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>4</v>
+      </c>
+      <c r="E182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12562,9 +13111,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>4</v>
+      </c>
+      <c r="E183" s="4">
         <v>2</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12663,9 +13215,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>2</v>
+      </c>
+      <c r="E184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12693,7 +13248,10 @@
       <c r="D185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>1</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12719,9 +13277,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>2</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12827,9 +13388,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>2</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12945,7 +13509,10 @@
       <c r="D188" s="4">
         <v>2</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="4">
+        <v>2</v>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13061,7 +13628,10 @@
       <c r="D189" s="4">
         <v>1</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>1</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13087,9 +13657,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>4</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13210,9 +13783,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>4</v>
+      </c>
+      <c r="E191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13333,9 +13909,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>4</v>
+      </c>
+      <c r="E192" s="4">
         <v>2</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13456,9 +14035,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>4</v>
+      </c>
+      <c r="E193" s="4">
         <v>3</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13581,7 +14163,10 @@
       <c r="D194" s="4">
         <v>4</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="4">
+        <v>4</v>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13702,9 +14287,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>6</v>
+      </c>
+      <c r="E195" s="4">
         <v>1</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13827,7 +14415,10 @@
       <c r="D196" s="4">
         <v>1</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="4">
+        <v>1</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13883,7 +14474,10 @@
       <c r="D197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="4">
+        <v>1</v>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13911,7 +14505,10 @@
       <c r="D198" s="4">
         <v>1</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>1</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13937,9 +14534,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>2</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14010,7 +14610,10 @@
       <c r="D200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="4">
+        <v>2</v>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14079,9 +14682,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>4</v>
+      </c>
+      <c r="E201" s="4">
         <v>1</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14157,9 +14763,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>4</v>
+      </c>
+      <c r="E202" s="4">
         <v>2</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14237,7 +14846,10 @@
       <c r="D203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>1</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14315,7 +14927,10 @@
       <c r="D204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="4">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14393,7 +15008,10 @@
       <c r="D205" s="4">
         <v>1</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="4">
+        <v>1</v>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14479,7 +15097,10 @@
       <c r="D206" s="4">
         <v>1</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="4">
+        <v>1</v>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14565,7 +15186,10 @@
       <c r="D207" s="4">
         <v>1</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="4">
+        <v>1</v>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14666,7 +15290,10 @@
       <c r="D208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>1</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14694,7 +15321,10 @@
       <c r="D209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14720,9 +15350,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>2</v>
+      </c>
+      <c r="E210" s="4">
         <v>1</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14748,9 +15381,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>3</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14864,9 +15500,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>3</v>
+      </c>
+      <c r="E212" s="4">
         <v>2</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14982,7 +15621,10 @@
       <c r="D213" s="4">
         <v>3</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="4">
+        <v>3</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15096,9 +15738,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>3</v>
+      </c>
+      <c r="E214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15219,9 +15864,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>3</v>
+      </c>
+      <c r="E215" s="4">
         <v>2</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15344,7 +15992,10 @@
       <c r="D216" s="4">
         <v>3</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="4">
+        <v>3</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15465,9 +16116,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>3</v>
+      </c>
+      <c r="E217" s="4">
         <v>1</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15588,9 +16242,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>3</v>
+      </c>
+      <c r="E218" s="4">
         <v>2</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15713,7 +16370,10 @@
       <c r="D219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15769,7 +16429,10 @@
       <c r="D220" s="4">
         <v>1</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15830,9 +16493,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>2</v>
+      </c>
+      <c r="E221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15910,7 +16576,10 @@
       <c r="D222" s="4">
         <v>1</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E222" s="4">
+        <v>1</v>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16001,9 +16670,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>3</v>
+      </c>
+      <c r="E223" s="4">
         <v>1</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16102,9 +16774,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>3</v>
+      </c>
+      <c r="E224" s="4">
         <v>2</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16203,9 +16878,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>2</v>
+      </c>
+      <c r="E225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16233,7 +16911,10 @@
       <c r="D226" s="4">
         <v>1</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>1</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16334,7 +17015,10 @@
       <c r="D227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E227" s="4">
+        <v>1</v>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16362,7 +17046,10 @@
       <c r="D228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="4">
+        <v>1</v>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16390,7 +17077,10 @@
       <c r="D229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="4">
+        <v>1</v>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16416,9 +17106,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>4</v>
+      </c>
+      <c r="E230" s="4">
         <v>1</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16534,7 +17227,10 @@
       <c r="D231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16648,9 +17344,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>6</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16764,9 +17463,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>6</v>
+      </c>
+      <c r="E233" s="4">
         <v>2</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16880,9 +17582,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>6</v>
+      </c>
+      <c r="E234" s="4">
         <v>3</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16996,9 +17701,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>2</v>
+      </c>
+      <c r="E235" s="4">
         <v>1</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17119,9 +17827,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>2</v>
+      </c>
+      <c r="E236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17244,7 +17955,10 @@
       <c r="D237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="4">
+        <v>1</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -17270,9 +17984,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>3</v>
+      </c>
+      <c r="E238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17326,9 +18043,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>3</v>
+      </c>
+      <c r="E239" s="4">
         <v>2</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17384,7 +18104,10 @@
       <c r="D240" s="4">
         <v>3</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="4">
+        <v>3</v>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17440,7 +18163,10 @@
       <c r="D241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="4">
+        <v>1</v>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17494,9 +18220,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>2</v>
+      </c>
+      <c r="E242" s="4">
         <v>1</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17552,7 +18281,10 @@
       <c r="D243" s="4">
         <v>2</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>2</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17608,7 +18340,10 @@
       <c r="D244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="4">
+        <v>1</v>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17662,9 +18397,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>2</v>
+      </c>
+      <c r="E245" s="4">
         <v>1</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17720,7 +18458,10 @@
       <c r="D246" s="4">
         <v>2</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="4">
+        <v>2</v>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17774,9 +18515,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>6</v>
+      </c>
+      <c r="E247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17830,9 +18574,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>6</v>
+      </c>
+      <c r="E248" s="4">
         <v>2</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17886,9 +18633,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>6</v>
+      </c>
+      <c r="E249" s="4">
         <v>3</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17942,9 +18692,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>6</v>
+      </c>
+      <c r="E250" s="4">
         <v>4</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17998,9 +18751,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>6</v>
+      </c>
+      <c r="E251" s="4">
         <v>5</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18056,7 +18812,10 @@
       <c r="D252" s="4">
         <v>6</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="4">
+        <v>6</v>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18110,9 +18869,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>4</v>
+      </c>
+      <c r="E253" s="4">
         <v>1</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18166,9 +18928,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>4</v>
+      </c>
+      <c r="E254" s="4">
         <v>2</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18222,9 +18987,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>4</v>
+      </c>
+      <c r="E255" s="4">
         <v>3</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18280,7 +19048,10 @@
       <c r="D256" s="4">
         <v>4</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="E256" s="4">
+        <v>4</v>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18334,9 +19105,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>3</v>
+      </c>
+      <c r="E257" s="4">
         <v>1</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18390,9 +19164,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>3</v>
+      </c>
+      <c r="E258" s="4">
         <v>2</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18448,7 +19225,10 @@
       <c r="D259" s="4">
         <v>3</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E259" s="4">
+        <v>3</v>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18502,9 +19282,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>4</v>
+      </c>
+      <c r="E260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18558,9 +19341,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>4</v>
+      </c>
+      <c r="E261" s="4">
         <v>2</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18614,9 +19400,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>4</v>
+      </c>
+      <c r="E262" s="4">
         <v>3</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18672,7 +19461,10 @@
       <c r="D263" s="4">
         <v>4</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="4">
+        <v>4</v>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18726,9 +19518,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>4</v>
+      </c>
+      <c r="E264" s="4">
         <v>1</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18782,9 +19577,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>4</v>
+      </c>
+      <c r="E265" s="4">
         <v>2</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18838,9 +19636,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>4</v>
+      </c>
+      <c r="E266" s="4">
         <v>3</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18896,7 +19697,10 @@
       <c r="D267" s="4">
         <v>4</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="4">
+        <v>4</v>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18950,9 +19754,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>3</v>
+      </c>
+      <c r="E268" s="4">
         <v>1</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19006,9 +19813,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>3</v>
+      </c>
+      <c r="E269" s="4">
         <v>2</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19064,7 +19874,10 @@
       <c r="D270" s="4">
         <v>3</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="4">
+        <v>3</v>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19118,9 +19931,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>3</v>
+      </c>
+      <c r="E271" s="4">
         <v>1</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19174,9 +19990,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>3</v>
+      </c>
+      <c r="E272" s="4">
         <v>2</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19232,7 +20051,10 @@
       <c r="D273" s="4">
         <v>3</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="4">
+        <v>3</v>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19286,9 +20108,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>3</v>
+      </c>
+      <c r="E274" s="4">
         <v>1</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19342,9 +20167,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>3</v>
+      </c>
+      <c r="E275" s="4">
         <v>2</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19400,7 +20228,10 @@
       <c r="D276" s="4">
         <v>3</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="4">
+        <v>3</v>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19454,9 +20285,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>6</v>
+      </c>
+      <c r="E277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19510,9 +20344,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>6</v>
+      </c>
+      <c r="E278" s="4">
         <v>2</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19566,9 +20403,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>6</v>
+      </c>
+      <c r="E279" s="4">
         <v>3</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19622,9 +20462,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>6</v>
+      </c>
+      <c r="E280" s="4">
         <v>4</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19678,9 +20521,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>6</v>
+      </c>
+      <c r="E281" s="4">
         <v>5</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19736,7 +20582,10 @@
       <c r="D282" s="4">
         <v>6</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="E282" s="4">
+        <v>6</v>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19790,9 +20639,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>5</v>
+      </c>
+      <c r="E283" s="4">
         <v>1</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19862,9 +20714,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>5</v>
+      </c>
+      <c r="E284" s="4">
         <v>2</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19934,9 +20789,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>5</v>
+      </c>
+      <c r="E285" s="4">
         <v>3</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20006,9 +20864,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>5</v>
+      </c>
+      <c r="E286" s="4">
         <v>4</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20080,7 +20941,10 @@
       <c r="D287" s="4">
         <v>5</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="4">
+        <v>5</v>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20152,7 +21016,10 @@
       <c r="D288" s="4">
         <v>1</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="E288" s="4">
+        <v>1</v>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20213,9 +21080,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>3</v>
+      </c>
+      <c r="E289" s="4">
         <v>1</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20284,9 +21154,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>3</v>
+      </c>
+      <c r="E290" s="4">
         <v>2</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20347,9 +21220,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>5</v>
+      </c>
+      <c r="E291" s="4">
         <v>1</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20410,9 +21286,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>5</v>
+      </c>
+      <c r="E292" s="4">
         <v>2</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20473,9 +21352,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>5</v>
+      </c>
+      <c r="E293" s="4">
         <v>3</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20536,9 +21418,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>5</v>
+      </c>
+      <c r="E294" s="4">
         <v>4</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20601,7 +21486,10 @@
       <c r="D295" s="4">
         <v>5</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="4">
+        <v>5</v>
+      </c>
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20662,9 +21550,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4">
         <v>1</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20733,9 +21624,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>4</v>
+      </c>
+      <c r="E297" s="4">
         <v>2</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20804,9 +21698,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>4</v>
+      </c>
+      <c r="E298" s="4">
         <v>3</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20877,7 +21774,10 @@
       <c r="D299" s="4">
         <v>4</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="4">
+        <v>4</v>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20948,7 +21848,10 @@
       <c r="D300" s="4">
         <v>1</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="4">
+        <v>1</v>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21024,9 +21927,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>104</v>
+      </c>
+      <c r="E301" s="4">
         <v>1</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21207,9 +22113,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>104</v>
+      </c>
+      <c r="E302" s="4">
         <v>2</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21353,9 +22262,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>104</v>
+      </c>
+      <c r="E303" s="4">
         <v>3</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21551,9 +22463,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>104</v>
+      </c>
+      <c r="E304" s="4">
         <v>4</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21674,9 +22589,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>104</v>
+      </c>
+      <c r="E305" s="4">
         <v>5</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21782,9 +22700,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>104</v>
+      </c>
+      <c r="E306" s="4">
         <v>6</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21898,9 +22819,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>104</v>
+      </c>
+      <c r="E307" s="4">
         <v>7</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22044,9 +22968,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>104</v>
+      </c>
+      <c r="E308" s="4">
         <v>8</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22152,9 +23079,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>104</v>
+      </c>
+      <c r="E309" s="4">
         <v>9</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22320,9 +23250,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>104</v>
+      </c>
+      <c r="E310" s="4">
         <v>10</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22458,9 +23391,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>104</v>
+      </c>
+      <c r="E311" s="4">
         <v>11</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22619,9 +23555,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>104</v>
+      </c>
+      <c r="E312" s="4">
         <v>12</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22817,9 +23756,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>104</v>
+      </c>
+      <c r="E313" s="4">
         <v>13</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22993,9 +23935,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>104</v>
+      </c>
+      <c r="E314" s="4">
         <v>14</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23109,9 +24054,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>104</v>
+      </c>
+      <c r="E315" s="4">
         <v>15</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23225,9 +24173,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>104</v>
+      </c>
+      <c r="E316" s="4">
         <v>16</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23341,9 +24292,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>104</v>
+      </c>
+      <c r="E317" s="4">
         <v>17</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23524,9 +24478,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>104</v>
+      </c>
+      <c r="E318" s="4">
         <v>18</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23647,9 +24604,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>104</v>
+      </c>
+      <c r="E319" s="4">
         <v>19</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23770,9 +24730,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>104</v>
+      </c>
+      <c r="E320" s="4">
         <v>20</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23880,7 +24843,10 @@
       <c r="D321" s="4">
         <v>1</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="4">
+        <v>1</v>
+      </c>
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23952,7 +24918,10 @@
       <c r="D322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="4">
+        <v>1</v>
+      </c>
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24013,9 +24982,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>4</v>
+      </c>
+      <c r="E323" s="4">
         <v>1</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24076,9 +25048,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>4</v>
+      </c>
+      <c r="E324" s="4">
         <v>2</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24139,9 +25114,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>4</v>
+      </c>
+      <c r="E325" s="4">
         <v>3</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24204,7 +25182,10 @@
       <c r="D326" s="4">
         <v>4</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="E326" s="4">
+        <v>4</v>
+      </c>
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24265,9 +25246,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>2</v>
+      </c>
+      <c r="E327" s="4">
         <v>1</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24338,7 +25322,10 @@
       <c r="D328" s="4">
         <v>2</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="E328" s="4">
+        <v>2</v>
+      </c>
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24409,7 +25396,10 @@
       <c r="D329" s="4">
         <v>1</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="4">
+        <v>1</v>
+      </c>
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24487,7 +25477,10 @@
       <c r="D330" s="4">
         <v>1</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="E330" s="4">
+        <v>1</v>
+      </c>
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24580,7 +25573,10 @@
       <c r="D331" s="4">
         <v>1</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="4">
+        <v>1</v>
+      </c>
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24651,7 +25647,10 @@
       <c r="D332" s="4">
         <v>1</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="4">
+        <v>1</v>
+      </c>
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24712,9 +25711,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>3</v>
+      </c>
+      <c r="E333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24813,9 +25815,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>3</v>
+      </c>
+      <c r="E334" s="4">
         <v>2</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24953,7 +25958,10 @@
       <c r="D335" s="4">
         <v>3</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="E335" s="4">
+        <v>3</v>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25076,7 +26084,10 @@
       <c r="D336" s="4">
         <v>1</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="E336" s="4">
+        <v>1</v>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25175,9 +26186,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>4</v>
+      </c>
+      <c r="E337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25247,9 +26261,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>4</v>
+      </c>
+      <c r="E338" s="4">
         <v>2</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25318,9 +26335,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>4</v>
+      </c>
+      <c r="E339" s="4">
         <v>3</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25398,7 +26418,10 @@
       <c r="D340" s="4">
         <v>4</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="E340" s="4">
+        <v>4</v>
+      </c>
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25474,9 +26497,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>2</v>
+      </c>
+      <c r="E341" s="4">
         <v>1</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25539,7 +26565,10 @@
       <c r="D342" s="4">
         <v>2</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="E342" s="4">
+        <v>2</v>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25600,9 +26629,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>18</v>
+      </c>
+      <c r="E343" s="4">
         <v>1</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25672,9 +26704,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>18</v>
+      </c>
+      <c r="E344" s="4">
         <v>2</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25744,9 +26779,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>18</v>
+      </c>
+      <c r="E345" s="4">
         <v>3</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25816,9 +26854,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>18</v>
+      </c>
+      <c r="E346" s="4">
         <v>4</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25888,9 +26929,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>18</v>
+      </c>
+      <c r="E347" s="4">
         <v>5</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25960,9 +27004,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>18</v>
+      </c>
+      <c r="E348" s="4">
         <v>6</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26032,9 +27079,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>18</v>
+      </c>
+      <c r="E349" s="4">
         <v>7</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26104,9 +27154,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>18</v>
+      </c>
+      <c r="E350" s="4">
         <v>8</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26176,9 +27229,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>18</v>
+      </c>
+      <c r="E351" s="4">
         <v>9</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26248,9 +27304,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>18</v>
+      </c>
+      <c r="E352" s="4">
         <v>10</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26320,9 +27379,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>18</v>
+      </c>
+      <c r="E353" s="4">
         <v>11</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26392,9 +27454,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>18</v>
+      </c>
+      <c r="E354" s="4">
         <v>12</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26464,9 +27529,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>18</v>
+      </c>
+      <c r="E355" s="4">
         <v>13</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26536,9 +27604,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>18</v>
+      </c>
+      <c r="E356" s="4">
         <v>14</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26608,9 +27679,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>18</v>
+      </c>
+      <c r="E357" s="4">
         <v>15</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26680,9 +27754,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>18</v>
+      </c>
+      <c r="E358" s="4">
         <v>16</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26752,9 +27829,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>18</v>
+      </c>
+      <c r="E359" s="4">
         <v>17</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26826,7 +27906,10 @@
       <c r="D360" s="4">
         <v>18</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="4">
+        <v>18</v>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26896,9 +27979,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>32</v>
+      </c>
+      <c r="E361" s="4">
         <v>1</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26968,9 +28054,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>32</v>
+      </c>
+      <c r="E362" s="4">
         <v>2</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27040,9 +28129,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>32</v>
+      </c>
+      <c r="E363" s="4">
         <v>3</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27112,9 +28204,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>32</v>
+      </c>
+      <c r="E364" s="4">
         <v>4</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27175,9 +28270,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>32</v>
+      </c>
+      <c r="E365" s="4">
         <v>5</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27247,9 +28345,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>32</v>
+      </c>
+      <c r="E366" s="4">
         <v>6</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27319,9 +28420,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>32</v>
+      </c>
+      <c r="E367" s="4">
         <v>7</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27391,9 +28495,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>32</v>
+      </c>
+      <c r="E368" s="4">
         <v>8</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27463,9 +28570,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>32</v>
+      </c>
+      <c r="E369" s="4">
         <v>9</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27535,9 +28645,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>32</v>
+      </c>
+      <c r="E370" s="4">
         <v>10</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27607,9 +28720,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>32</v>
+      </c>
+      <c r="E371" s="4">
         <v>11</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27679,9 +28795,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>32</v>
+      </c>
+      <c r="E372" s="4">
         <v>12</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27751,9 +28870,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>32</v>
+      </c>
+      <c r="E373" s="4">
         <v>13</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27823,9 +28945,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>32</v>
+      </c>
+      <c r="E374" s="4">
         <v>14</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27895,9 +29020,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>32</v>
+      </c>
+      <c r="E375" s="4">
         <v>15</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27967,9 +29095,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>32</v>
+      </c>
+      <c r="E376" s="4">
         <v>16</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28039,9 +29170,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>32</v>
+      </c>
+      <c r="E377" s="4">
         <v>17</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28111,9 +29245,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>32</v>
+      </c>
+      <c r="E378" s="4">
         <v>18</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28183,9 +29320,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>32</v>
+      </c>
+      <c r="E379" s="4">
         <v>19</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28255,9 +29395,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>32</v>
+      </c>
+      <c r="E380" s="4">
         <v>20</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28329,7 +29472,10 @@
       <c r="D381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="E381" s="4">
+        <v>1</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28383,9 +29529,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>7</v>
+      </c>
+      <c r="E382" s="4">
         <v>1</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28439,9 +29588,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>7</v>
+      </c>
+      <c r="E383" s="4">
         <v>2</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28495,9 +29647,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>7</v>
+      </c>
+      <c r="E384" s="4">
         <v>3</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28551,9 +29706,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>7</v>
+      </c>
+      <c r="E385" s="4">
         <v>4</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28607,9 +29765,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>7</v>
+      </c>
+      <c r="E386" s="4">
         <v>5</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28663,9 +29824,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>7</v>
+      </c>
+      <c r="E387" s="4">
         <v>6</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28721,7 +29885,10 @@
       <c r="D388" s="4">
         <v>7</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="4">
+        <v>7</v>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28777,7 +29944,10 @@
       <c r="D389" s="4">
         <v>1</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="E389" s="4">
+        <v>1</v>
+      </c>
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28833,7 +30003,10 @@
       <c r="D390" s="4">
         <v>1</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="4">
+        <v>1</v>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28887,9 +30060,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>3</v>
+      </c>
+      <c r="E391" s="4">
         <v>1</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28943,9 +30119,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>3</v>
+      </c>
+      <c r="E392" s="4">
         <v>2</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29001,7 +30180,10 @@
       <c r="D393" s="4">
         <v>3</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E393" s="4">
+        <v>3</v>
+      </c>
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29055,9 +30237,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>45</v>
+      </c>
+      <c r="E394" s="4">
         <v>1</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29111,9 +30296,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>45</v>
+      </c>
+      <c r="E395" s="4">
         <v>2</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29167,9 +30355,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>45</v>
+      </c>
+      <c r="E396" s="4">
         <v>3</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29223,9 +30414,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>45</v>
+      </c>
+      <c r="E397" s="4">
         <v>4</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29279,9 +30473,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>45</v>
+      </c>
+      <c r="E398" s="4">
         <v>5</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29335,9 +30532,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>45</v>
+      </c>
+      <c r="E399" s="4">
         <v>6</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29391,9 +30591,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>45</v>
+      </c>
+      <c r="E400" s="4">
         <v>7</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29447,9 +30650,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>45</v>
+      </c>
+      <c r="E401" s="4">
         <v>8</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29503,9 +30709,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>45</v>
+      </c>
+      <c r="E402" s="4">
         <v>9</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29559,9 +30768,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>45</v>
+      </c>
+      <c r="E403" s="4">
         <v>10</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29615,9 +30827,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>45</v>
+      </c>
+      <c r="E404" s="4">
         <v>11</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29671,9 +30886,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>45</v>
+      </c>
+      <c r="E405" s="4">
         <v>12</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29727,9 +30945,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>45</v>
+      </c>
+      <c r="E406" s="4">
         <v>13</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29783,9 +31004,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>45</v>
+      </c>
+      <c r="E407" s="4">
         <v>14</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29839,9 +31063,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>45</v>
+      </c>
+      <c r="E408" s="4">
         <v>15</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29895,9 +31122,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>45</v>
+      </c>
+      <c r="E409" s="4">
         <v>16</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29951,9 +31181,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>45</v>
+      </c>
+      <c r="E410" s="4">
         <v>17</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30007,9 +31240,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>45</v>
+      </c>
+      <c r="E411" s="4">
         <v>18</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30063,9 +31299,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>45</v>
+      </c>
+      <c r="E412" s="4">
         <v>19</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30119,9 +31358,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>45</v>
+      </c>
+      <c r="E413" s="4">
         <v>20</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30177,7 +31419,10 @@
       <c r="D414" s="4">
         <v>1</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="E414" s="4">
+        <v>1</v>
+      </c>
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30249,7 +31494,10 @@
       <c r="D415" s="4">
         <v>1</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="E415" s="4">
+        <v>1</v>
+      </c>
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30310,9 +31558,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>2</v>
+      </c>
+      <c r="E416" s="4">
         <v>1</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30413,7 +31664,10 @@
       <c r="D417" s="4">
         <v>2</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="E417" s="4">
+        <v>2</v>
+      </c>
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30497,9 +31751,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>2</v>
+      </c>
+      <c r="E418" s="4">
         <v>1</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30562,7 +31819,10 @@
       <c r="D419" s="4">
         <v>2</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="4">
+        <v>2</v>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30625,7 +31885,10 @@
       <c r="D420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="E420" s="4">
+        <v>1</v>
+      </c>
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30696,7 +31959,10 @@
       <c r="D421" s="4">
         <v>1</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="4">
+        <v>1</v>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30772,9 +32038,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>2</v>
+      </c>
+      <c r="E422" s="4">
         <v>1</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30860,7 +32129,10 @@
       <c r="D423" s="4">
         <v>2</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="4">
+        <v>2</v>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30944,9 +32216,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>32</v>
+      </c>
+      <c r="E424" s="4">
         <v>1</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31090,9 +32365,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>32</v>
+      </c>
+      <c r="E425" s="4">
         <v>2</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31258,9 +32536,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>32</v>
+      </c>
+      <c r="E426" s="4">
         <v>3</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31411,9 +32692,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>32</v>
+      </c>
+      <c r="E427" s="4">
         <v>4</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31542,9 +32826,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>32</v>
+      </c>
+      <c r="E428" s="4">
         <v>5</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31703,9 +32990,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>32</v>
+      </c>
+      <c r="E429" s="4">
         <v>6</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31804,9 +33094,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>32</v>
+      </c>
+      <c r="E430" s="4">
         <v>7</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31927,9 +33220,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>32</v>
+      </c>
+      <c r="E431" s="4">
         <v>8</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32058,9 +33354,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>32</v>
+      </c>
+      <c r="E432" s="4">
         <v>9</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32219,9 +33518,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>32</v>
+      </c>
+      <c r="E433" s="4">
         <v>10</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32417,9 +33719,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>32</v>
+      </c>
+      <c r="E434" s="4">
         <v>11</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32615,9 +33920,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>32</v>
+      </c>
+      <c r="E435" s="4">
         <v>12</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32783,9 +34091,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>32</v>
+      </c>
+      <c r="E436" s="4">
         <v>13</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32951,9 +34262,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>32</v>
+      </c>
+      <c r="E437" s="4">
         <v>14</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33052,9 +34366,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>32</v>
+      </c>
+      <c r="E438" s="4">
         <v>15</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33175,9 +34492,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>32</v>
+      </c>
+      <c r="E439" s="4">
         <v>16</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33276,9 +34596,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>32</v>
+      </c>
+      <c r="E440" s="4">
         <v>17</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33437,9 +34760,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>32</v>
+      </c>
+      <c r="E441" s="4">
         <v>18</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33598,9 +34924,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>32</v>
+      </c>
+      <c r="E442" s="4">
         <v>19</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33714,9 +35043,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>32</v>
+      </c>
+      <c r="E443" s="4">
         <v>20</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33852,9 +35184,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>3</v>
+      </c>
+      <c r="E444" s="4">
         <v>1</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33924,9 +35259,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>3</v>
+      </c>
+      <c r="E445" s="4">
         <v>2</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33998,7 +35336,10 @@
       <c r="D446" s="4">
         <v>3</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="E446" s="4">
+        <v>3</v>
+      </c>
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34068,9 +35409,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>3</v>
+      </c>
+      <c r="E447" s="4">
         <v>1</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34131,9 +35475,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>3</v>
+      </c>
+      <c r="E448" s="4">
         <v>2</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34196,7 +35543,10 @@
       <c r="D449" s="4">
         <v>3</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="4">
+        <v>3</v>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34259,7 +35609,10 @@
       <c r="D450" s="4">
         <v>1</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="E450" s="4">
+        <v>1</v>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34375,7 +35728,10 @@
       <c r="D451" s="4">
         <v>1</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="E451" s="4">
+        <v>1</v>
+      </c>
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34436,9 +35792,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>2</v>
+      </c>
+      <c r="E452" s="4">
         <v>1</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34501,7 +35860,10 @@
       <c r="D453" s="4">
         <v>2</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="E453" s="4">
+        <v>2</v>
+      </c>
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34562,9 +35924,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>2</v>
+      </c>
+      <c r="E454" s="4">
         <v>1</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34635,7 +36000,10 @@
       <c r="D455" s="4">
         <v>2</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="E455" s="4">
+        <v>2</v>
+      </c>
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34706,7 +36074,10 @@
       <c r="D456" s="4">
         <v>1</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="E456" s="4">
+        <v>1</v>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34790,9 +36161,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>3</v>
+      </c>
+      <c r="E457" s="4">
         <v>1</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34951,9 +36325,12 @@
         </is>
       </c>
       <c r="D458" s="4">
+        <v>3</v>
+      </c>
+      <c r="E458" s="4">
         <v>2</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35114,7 +36491,10 @@
       <c r="D459" s="4">
         <v>3</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="E459" s="4">
+        <v>3</v>
+      </c>
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35252,7 +36632,10 @@
       <c r="D460" s="4">
         <v>1</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="E460" s="4">
+        <v>1</v>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35322,9 +36705,12 @@
         </is>
       </c>
       <c r="D461" s="4">
+        <v>5</v>
+      </c>
+      <c r="E461" s="4">
         <v>1</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35385,9 +36771,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>5</v>
+      </c>
+      <c r="E462" s="4">
         <v>2</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35448,9 +36837,12 @@
         </is>
       </c>
       <c r="D463" s="4">
+        <v>5</v>
+      </c>
+      <c r="E463" s="4">
         <v>3</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35520,9 +36912,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>5</v>
+      </c>
+      <c r="E464" s="4">
         <v>4</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35593,7 +36988,10 @@
       <c r="D465" s="4">
         <v>5</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="E465" s="4">
+        <v>5</v>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35662,9 +37060,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>17</v>
+      </c>
+      <c r="E466" s="4">
         <v>1</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35725,9 +37126,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>17</v>
+      </c>
+      <c r="E467" s="4">
         <v>2</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35788,9 +37192,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>17</v>
+      </c>
+      <c r="E468" s="4">
         <v>3</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35851,9 +37258,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>17</v>
+      </c>
+      <c r="E469" s="4">
         <v>4</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35914,9 +37324,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>17</v>
+      </c>
+      <c r="E470" s="4">
         <v>5</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35977,9 +37390,12 @@
         </is>
       </c>
       <c r="D471" s="4">
+        <v>17</v>
+      </c>
+      <c r="E471" s="4">
         <v>6</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36040,9 +37456,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>17</v>
+      </c>
+      <c r="E472" s="4">
         <v>7</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36103,9 +37522,12 @@
         </is>
       </c>
       <c r="D473" s="4">
+        <v>17</v>
+      </c>
+      <c r="E473" s="4">
         <v>8</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36166,9 +37588,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>17</v>
+      </c>
+      <c r="E474" s="4">
         <v>9</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36229,9 +37654,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>17</v>
+      </c>
+      <c r="E475" s="4">
         <v>10</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36292,9 +37720,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>17</v>
+      </c>
+      <c r="E476" s="4">
         <v>11</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36355,9 +37786,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>17</v>
+      </c>
+      <c r="E477" s="4">
         <v>12</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36418,9 +37852,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>17</v>
+      </c>
+      <c r="E478" s="4">
         <v>13</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36481,9 +37918,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>17</v>
+      </c>
+      <c r="E479" s="4">
         <v>14</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36544,9 +37984,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>17</v>
+      </c>
+      <c r="E480" s="4">
         <v>15</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36607,9 +38050,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>17</v>
+      </c>
+      <c r="E481" s="4">
         <v>16</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36672,7 +38118,10 @@
       <c r="D482" s="4">
         <v>17</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="E482" s="4">
+        <v>17</v>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36733,9 +38182,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>5</v>
+      </c>
+      <c r="E483" s="4">
         <v>1</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36834,9 +38286,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>5</v>
+      </c>
+      <c r="E484" s="4">
         <v>2</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36927,9 +38382,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>5</v>
+      </c>
+      <c r="E485" s="4">
         <v>3</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36990,9 +38448,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>5</v>
+      </c>
+      <c r="E486" s="4">
         <v>4</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37055,7 +38516,10 @@
       <c r="D487" s="4">
         <v>5</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="E487" s="4">
+        <v>5</v>
+      </c>
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37141,7 +38605,10 @@
       <c r="D488" s="4">
         <v>1</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="E488" s="4">
+        <v>1</v>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37211,9 +38678,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>2</v>
+      </c>
+      <c r="E489" s="4">
         <v>1</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37285,7 +38755,10 @@
       <c r="D490" s="4">
         <v>2</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="E490" s="4">
+        <v>2</v>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37355,9 +38828,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>6</v>
+      </c>
+      <c r="E491" s="4">
         <v>1</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37427,9 +38903,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>6</v>
+      </c>
+      <c r="E492" s="4">
         <v>2</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37499,9 +38978,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>6</v>
+      </c>
+      <c r="E493" s="4">
         <v>3</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37562,9 +39044,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>6</v>
+      </c>
+      <c r="E494" s="4">
         <v>4</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37634,9 +39119,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>6</v>
+      </c>
+      <c r="E495" s="4">
         <v>5</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37699,7 +39187,10 @@
       <c r="D496" s="4">
         <v>6</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="E496" s="4">
+        <v>6</v>
+      </c>
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37771,7 +39262,10 @@
       <c r="D497" s="4">
         <v>1</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="E497" s="4">
+        <v>1</v>
+      </c>
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37841,9 +39335,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>2</v>
+      </c>
+      <c r="E498" s="4">
         <v>1</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37915,7 +39412,10 @@
       <c r="D499" s="4">
         <v>2</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="E499" s="4">
+        <v>2</v>
+      </c>
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37987,7 +39487,10 @@
       <c r="D500" s="4">
         <v>1</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="E500" s="4">
+        <v>1</v>
+      </c>
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38059,7 +39562,10 @@
       <c r="D501" s="4">
         <v>1</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="E501" s="4">
+        <v>1</v>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38131,7 +39637,10 @@
       <c r="D502" s="4">
         <v>1</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="E502" s="4">
+        <v>1</v>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38201,9 +39710,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>2</v>
+      </c>
+      <c r="E503" s="4">
         <v>1</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38275,7 +39787,10 @@
       <c r="D504" s="4">
         <v>2</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="E504" s="4">
+        <v>2</v>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38347,7 +39862,10 @@
       <c r="D505" s="4">
         <v>1</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="E505" s="4">
+        <v>1</v>
+      </c>
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38417,9 +39935,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>2</v>
+      </c>
+      <c r="E506" s="4">
         <v>1</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38491,7 +40012,10 @@
       <c r="D507" s="4">
         <v>2</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="E507" s="4">
+        <v>2</v>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38561,9 +40085,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>6</v>
+      </c>
+      <c r="E508" s="4">
         <v>1</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38633,9 +40160,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>6</v>
+      </c>
+      <c r="E509" s="4">
         <v>2</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38705,9 +40235,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>6</v>
+      </c>
+      <c r="E510" s="4">
         <v>3</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38777,9 +40310,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>6</v>
+      </c>
+      <c r="E511" s="4">
         <v>4</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38849,9 +40385,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>6</v>
+      </c>
+      <c r="E512" s="4">
         <v>5</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38923,7 +40462,10 @@
       <c r="D513" s="4">
         <v>6</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="E513" s="4">
+        <v>6</v>
+      </c>
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38993,9 +40535,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>2</v>
+      </c>
+      <c r="E514" s="4">
         <v>1</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39067,7 +40612,10 @@
       <c r="D515" s="4">
         <v>2</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="E515" s="4">
+        <v>2</v>
+      </c>
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39137,9 +40685,12 @@
         </is>
       </c>
       <c r="D516" s="4">
+        <v>2</v>
+      </c>
+      <c r="E516" s="4">
         <v>1</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39211,7 +40762,10 @@
       <c r="D517" s="4">
         <v>2</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="E517" s="4">
+        <v>2</v>
+      </c>
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39283,7 +40837,10 @@
       <c r="D518" s="4">
         <v>1</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="4">
+        <v>1</v>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39355,7 +40912,10 @@
       <c r="D519" s="4">
         <v>1</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="E519" s="4">
+        <v>1</v>
+      </c>
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39427,7 +40987,10 @@
       <c r="D520" s="4">
         <v>1</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="E520" s="4">
+        <v>1</v>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39481,283 +41044,375 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="276">
+  <mergeCells count="368">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="C21:C25"/>
+    <mergeCell ref="D21:D25"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="C27:C31"/>
+    <mergeCell ref="D27:D31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="A36:A38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="B41:B45"/>
     <mergeCell ref="C41:C45"/>
+    <mergeCell ref="D41:D45"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D46:D49"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="B61:B62"/>
     <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
     <mergeCell ref="A65:A69"/>
     <mergeCell ref="B65:B69"/>
     <mergeCell ref="C65:C69"/>
+    <mergeCell ref="D65:D69"/>
     <mergeCell ref="A72:A76"/>
     <mergeCell ref="B72:B76"/>
     <mergeCell ref="C72:C76"/>
+    <mergeCell ref="D72:D76"/>
     <mergeCell ref="A77:A78"/>
     <mergeCell ref="B77:B78"/>
     <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
     <mergeCell ref="A79:A83"/>
     <mergeCell ref="B79:B83"/>
     <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
     <mergeCell ref="A84:A85"/>
     <mergeCell ref="B84:B85"/>
     <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
     <mergeCell ref="A86:A87"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
     <mergeCell ref="A88:A89"/>
     <mergeCell ref="B88:B89"/>
     <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="B92:B93"/>
     <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="A100:A104"/>
     <mergeCell ref="B100:B104"/>
     <mergeCell ref="C100:C104"/>
+    <mergeCell ref="D100:D104"/>
     <mergeCell ref="A106:A110"/>
     <mergeCell ref="B106:B110"/>
     <mergeCell ref="C106:C110"/>
+    <mergeCell ref="D106:D110"/>
     <mergeCell ref="A111:A112"/>
     <mergeCell ref="B111:B112"/>
     <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:D112"/>
     <mergeCell ref="A113:A115"/>
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
     <mergeCell ref="A120:A121"/>
     <mergeCell ref="B120:B121"/>
     <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
     <mergeCell ref="A139:A140"/>
     <mergeCell ref="B139:B140"/>
     <mergeCell ref="C139:C140"/>
+    <mergeCell ref="D139:D140"/>
     <mergeCell ref="A148:A151"/>
     <mergeCell ref="B148:B151"/>
     <mergeCell ref="C148:C151"/>
+    <mergeCell ref="D148:D151"/>
     <mergeCell ref="A153:A154"/>
     <mergeCell ref="B153:B154"/>
     <mergeCell ref="C153:C154"/>
+    <mergeCell ref="D153:D154"/>
     <mergeCell ref="A157:A158"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
     <mergeCell ref="A161:A163"/>
     <mergeCell ref="B161:B163"/>
     <mergeCell ref="C161:C163"/>
+    <mergeCell ref="D161:D163"/>
     <mergeCell ref="A167:A171"/>
     <mergeCell ref="B167:B171"/>
     <mergeCell ref="C167:C171"/>
+    <mergeCell ref="D167:D171"/>
     <mergeCell ref="A172:A176"/>
     <mergeCell ref="B172:B176"/>
     <mergeCell ref="C172:C176"/>
+    <mergeCell ref="D172:D176"/>
     <mergeCell ref="A177:A178"/>
     <mergeCell ref="B177:B178"/>
     <mergeCell ref="C177:C178"/>
+    <mergeCell ref="D177:D178"/>
     <mergeCell ref="A182:A183"/>
     <mergeCell ref="B182:B183"/>
     <mergeCell ref="C182:C183"/>
+    <mergeCell ref="D182:D183"/>
     <mergeCell ref="A187:A188"/>
     <mergeCell ref="B187:B188"/>
     <mergeCell ref="C187:C188"/>
+    <mergeCell ref="D187:D188"/>
     <mergeCell ref="A191:A194"/>
     <mergeCell ref="B191:B194"/>
     <mergeCell ref="C191:C194"/>
+    <mergeCell ref="D191:D194"/>
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="B199:B200"/>
     <mergeCell ref="C199:C200"/>
+    <mergeCell ref="D199:D200"/>
     <mergeCell ref="A201:A202"/>
     <mergeCell ref="B201:B202"/>
     <mergeCell ref="C201:C202"/>
+    <mergeCell ref="D201:D202"/>
     <mergeCell ref="A211:A213"/>
     <mergeCell ref="B211:B213"/>
     <mergeCell ref="C211:C213"/>
+    <mergeCell ref="D211:D213"/>
     <mergeCell ref="A214:A216"/>
     <mergeCell ref="B214:B216"/>
     <mergeCell ref="C214:C216"/>
+    <mergeCell ref="D214:D216"/>
     <mergeCell ref="A217:A218"/>
     <mergeCell ref="B217:B218"/>
     <mergeCell ref="C217:C218"/>
+    <mergeCell ref="D217:D218"/>
     <mergeCell ref="A223:A224"/>
     <mergeCell ref="B223:B224"/>
     <mergeCell ref="C223:C224"/>
+    <mergeCell ref="D223:D224"/>
     <mergeCell ref="A232:A234"/>
     <mergeCell ref="B232:B234"/>
     <mergeCell ref="C232:C234"/>
+    <mergeCell ref="D232:D234"/>
     <mergeCell ref="A238:A240"/>
     <mergeCell ref="B238:B240"/>
     <mergeCell ref="C238:C240"/>
+    <mergeCell ref="D238:D240"/>
     <mergeCell ref="A242:A243"/>
     <mergeCell ref="B242:B243"/>
     <mergeCell ref="C242:C243"/>
+    <mergeCell ref="D242:D243"/>
     <mergeCell ref="A245:A246"/>
     <mergeCell ref="B245:B246"/>
     <mergeCell ref="C245:C246"/>
+    <mergeCell ref="D245:D246"/>
     <mergeCell ref="A247:A252"/>
     <mergeCell ref="B247:B252"/>
     <mergeCell ref="C247:C252"/>
+    <mergeCell ref="D247:D252"/>
     <mergeCell ref="A253:A256"/>
     <mergeCell ref="B253:B256"/>
     <mergeCell ref="C253:C256"/>
+    <mergeCell ref="D253:D256"/>
     <mergeCell ref="A257:A259"/>
     <mergeCell ref="B257:B259"/>
     <mergeCell ref="C257:C259"/>
+    <mergeCell ref="D257:D259"/>
     <mergeCell ref="A260:A263"/>
     <mergeCell ref="B260:B263"/>
     <mergeCell ref="C260:C263"/>
+    <mergeCell ref="D260:D263"/>
     <mergeCell ref="A264:A267"/>
     <mergeCell ref="B264:B267"/>
     <mergeCell ref="C264:C267"/>
+    <mergeCell ref="D264:D267"/>
     <mergeCell ref="A268:A270"/>
     <mergeCell ref="B268:B270"/>
     <mergeCell ref="C268:C270"/>
+    <mergeCell ref="D268:D270"/>
     <mergeCell ref="A271:A273"/>
     <mergeCell ref="B271:B273"/>
     <mergeCell ref="C271:C273"/>
+    <mergeCell ref="D271:D273"/>
     <mergeCell ref="A274:A276"/>
     <mergeCell ref="B274:B276"/>
     <mergeCell ref="C274:C276"/>
+    <mergeCell ref="D274:D276"/>
     <mergeCell ref="A277:A282"/>
     <mergeCell ref="B277:B282"/>
     <mergeCell ref="C277:C282"/>
+    <mergeCell ref="D277:D282"/>
     <mergeCell ref="A283:A287"/>
     <mergeCell ref="B283:B287"/>
     <mergeCell ref="C283:C287"/>
+    <mergeCell ref="D283:D287"/>
     <mergeCell ref="A289:A290"/>
     <mergeCell ref="B289:B290"/>
     <mergeCell ref="C289:C290"/>
+    <mergeCell ref="D289:D290"/>
     <mergeCell ref="A291:A295"/>
     <mergeCell ref="B291:B295"/>
     <mergeCell ref="C291:C295"/>
+    <mergeCell ref="D291:D295"/>
     <mergeCell ref="A296:A299"/>
     <mergeCell ref="B296:B299"/>
     <mergeCell ref="C296:C299"/>
+    <mergeCell ref="D296:D299"/>
     <mergeCell ref="A301:A320"/>
     <mergeCell ref="B301:B320"/>
     <mergeCell ref="C301:C320"/>
+    <mergeCell ref="D301:D320"/>
     <mergeCell ref="A323:A326"/>
     <mergeCell ref="B323:B326"/>
     <mergeCell ref="C323:C326"/>
+    <mergeCell ref="D323:D326"/>
     <mergeCell ref="A327:A328"/>
     <mergeCell ref="B327:B328"/>
     <mergeCell ref="C327:C328"/>
+    <mergeCell ref="D327:D328"/>
     <mergeCell ref="A333:A335"/>
     <mergeCell ref="B333:B335"/>
     <mergeCell ref="C333:C335"/>
+    <mergeCell ref="D333:D335"/>
     <mergeCell ref="A337:A340"/>
     <mergeCell ref="B337:B340"/>
     <mergeCell ref="C337:C340"/>
+    <mergeCell ref="D337:D340"/>
     <mergeCell ref="A341:A342"/>
     <mergeCell ref="B341:B342"/>
     <mergeCell ref="C341:C342"/>
+    <mergeCell ref="D341:D342"/>
     <mergeCell ref="A343:A360"/>
     <mergeCell ref="B343:B360"/>
     <mergeCell ref="C343:C360"/>
+    <mergeCell ref="D343:D360"/>
     <mergeCell ref="A361:A380"/>
     <mergeCell ref="B361:B380"/>
     <mergeCell ref="C361:C380"/>
+    <mergeCell ref="D361:D380"/>
     <mergeCell ref="A382:A388"/>
     <mergeCell ref="B382:B388"/>
     <mergeCell ref="C382:C388"/>
+    <mergeCell ref="D382:D388"/>
     <mergeCell ref="A391:A393"/>
     <mergeCell ref="B391:B393"/>
     <mergeCell ref="C391:C393"/>
+    <mergeCell ref="D391:D393"/>
     <mergeCell ref="A394:A413"/>
     <mergeCell ref="B394:B413"/>
     <mergeCell ref="C394:C413"/>
+    <mergeCell ref="D394:D413"/>
     <mergeCell ref="A416:A417"/>
     <mergeCell ref="B416:B417"/>
     <mergeCell ref="C416:C417"/>
+    <mergeCell ref="D416:D417"/>
     <mergeCell ref="A418:A419"/>
     <mergeCell ref="B418:B419"/>
     <mergeCell ref="C418:C419"/>
+    <mergeCell ref="D418:D419"/>
     <mergeCell ref="A422:A423"/>
     <mergeCell ref="B422:B423"/>
     <mergeCell ref="C422:C423"/>
+    <mergeCell ref="D422:D423"/>
     <mergeCell ref="A424:A443"/>
     <mergeCell ref="B424:B443"/>
     <mergeCell ref="C424:C443"/>
+    <mergeCell ref="D424:D443"/>
     <mergeCell ref="A444:A446"/>
     <mergeCell ref="B444:B446"/>
     <mergeCell ref="C444:C446"/>
+    <mergeCell ref="D444:D446"/>
     <mergeCell ref="A447:A449"/>
     <mergeCell ref="B447:B449"/>
     <mergeCell ref="C447:C449"/>
+    <mergeCell ref="D447:D449"/>
     <mergeCell ref="A452:A453"/>
     <mergeCell ref="B452:B453"/>
     <mergeCell ref="C452:C453"/>
+    <mergeCell ref="D452:D453"/>
     <mergeCell ref="A454:A455"/>
     <mergeCell ref="B454:B455"/>
     <mergeCell ref="C454:C455"/>
+    <mergeCell ref="D454:D455"/>
     <mergeCell ref="A457:A459"/>
     <mergeCell ref="B457:B459"/>
     <mergeCell ref="C457:C459"/>
+    <mergeCell ref="D457:D459"/>
     <mergeCell ref="A461:A465"/>
     <mergeCell ref="B461:B465"/>
     <mergeCell ref="C461:C465"/>
+    <mergeCell ref="D461:D465"/>
     <mergeCell ref="A466:A482"/>
     <mergeCell ref="B466:B482"/>
     <mergeCell ref="C466:C482"/>
+    <mergeCell ref="D466:D482"/>
     <mergeCell ref="A483:A487"/>
     <mergeCell ref="B483:B487"/>
     <mergeCell ref="C483:C487"/>
+    <mergeCell ref="D483:D487"/>
     <mergeCell ref="A489:A490"/>
     <mergeCell ref="B489:B490"/>
     <mergeCell ref="C489:C490"/>
+    <mergeCell ref="D489:D490"/>
     <mergeCell ref="A491:A496"/>
     <mergeCell ref="B491:B496"/>
     <mergeCell ref="C491:C496"/>
+    <mergeCell ref="D491:D496"/>
     <mergeCell ref="A498:A499"/>
     <mergeCell ref="B498:B499"/>
     <mergeCell ref="C498:C499"/>
+    <mergeCell ref="D498:D499"/>
     <mergeCell ref="A503:A504"/>
     <mergeCell ref="B503:B504"/>
     <mergeCell ref="C503:C504"/>
+    <mergeCell ref="D503:D504"/>
     <mergeCell ref="A506:A507"/>
     <mergeCell ref="B506:B507"/>
     <mergeCell ref="C506:C507"/>
+    <mergeCell ref="D506:D507"/>
     <mergeCell ref="A508:A513"/>
     <mergeCell ref="B508:B513"/>
     <mergeCell ref="C508:C513"/>
+    <mergeCell ref="D508:D513"/>
     <mergeCell ref="A514:A515"/>
     <mergeCell ref="B514:B515"/>
     <mergeCell ref="C514:C515"/>
+    <mergeCell ref="D514:D515"/>
     <mergeCell ref="A516:A517"/>
     <mergeCell ref="B516:B517"/>
     <mergeCell ref="C516:C517"/>
+    <mergeCell ref="D516:D517"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
